--- a/lcoe/liquid_fuels/ethanol_upgrade_lcoe/LCOE_ETHANOL_UPGRADE_1.xlsx
+++ b/lcoe/liquid_fuels/ethanol_upgrade_lcoe/LCOE_ETHANOL_UPGRADE_1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lc_detailed" sheetId="1" state="visible" r:id="rId1"/>
@@ -21085,12 +21085,12 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>h2_consumption - ethanol upgrade</t>
+          <t>h2_consumption</t>
         </is>
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>elec_consumption - ethanol upgrade</t>
+          <t>elec_consumption</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>elec_production - ethanol upgrade</t>
+          <t>elec_production</t>
         </is>
       </c>
       <c r="F2" s="19" t="inlineStr">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="I2" s="19" t="inlineStr">
         <is>
-          <t>investment_cost - ethanol upgrade</t>
+          <t>investment_cost</t>
         </is>
       </c>
       <c r="J2" s="19" t="inlineStr">
@@ -21130,7 +21130,7 @@
       </c>
       <c r="K2" s="19" t="inlineStr">
         <is>
-          <t>fixed_om_cost - ethanol upgrade</t>
+          <t>fixed_om_cost</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="M2" s="19" t="inlineStr">
         <is>
-          <t>variable_om_cost - ethanol upgrade</t>
+          <t>variable_om_cost</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
